--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124451765</v>
+        <v>124450561</v>
       </c>
       <c r="B2" t="n">
-        <v>79795</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,26 +713,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388100</v>
+        <v>388163</v>
       </c>
       <c r="R2" t="n">
-        <v>6611571</v>
+        <v>6611530</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,7 +770,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,12 +780,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 bålar på en asp.</t>
+          <t>Revirhävdande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124450561</v>
+        <v>124451765</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>79795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,25 +824,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,35 +850,26 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388163</v>
+        <v>388100</v>
       </c>
       <c r="R3" t="n">
-        <v>6611530</v>
+        <v>6611571</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Revirhävdande</t>
+          <t>2 bålar på en asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124450561</v>
+        <v>124451765</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>79795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,35 +713,26 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388163</v>
+        <v>388100</v>
       </c>
       <c r="R2" t="n">
-        <v>6611530</v>
+        <v>6611571</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -780,12 +771,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Revirhävdande</t>
+          <t>2 bålar på en asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124451765</v>
+        <v>124450561</v>
       </c>
       <c r="B3" t="n">
-        <v>79795</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,25 +815,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,26 +841,35 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388100</v>
+        <v>388163</v>
       </c>
       <c r="R3" t="n">
-        <v>6611571</v>
+        <v>6611530</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 bålar på en asp.</t>
+          <t>Revirhävdande</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,6 +938,127 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128504651</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>388188</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6611467</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikliga mänger utefter bäckdråget. Överblommade.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bäckdråg i skött barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>128504651</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>128504651</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>128504651</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>128504651</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>128504651</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>128504651</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>128504651</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2024 artfynd.xlsx
+++ b/artfynd/A 21248-2024 artfynd.xlsx
@@ -943,7 +943,7 @@
         <v>128504651</v>
       </c>
       <c r="B4" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
